--- a/docs/go_live_regression_execution_template.xlsx
+++ b/docs/go_live_regression_execution_template.xlsx
@@ -1456,12 +1456,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Flyway</t>
+          <t>上线初始化</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>目标环境执行 Flyway 后，确认 V20260402_012/013/014 迁移按顺序成功</t>
+          <t>目标环境按上线初始化脚本完成库表、菜单、字典、权限与必要基础数据初始化，正式上线包不依赖 Flyway 运行期迁移</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>待环境验证</t>
+          <t>待执行</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
